--- a/PROJECT MAOLIN New/Craveva full inventory.xlsx
+++ b/PROJECT MAOLIN New/Craveva full inventory.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\web\craveva-staging\PROJECT MAOLIN New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DF7A54-93D7-4DC1-83AA-F7BA9A2D9A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1229291-BF28-416E-87E3-68D828BFE173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="庫存明細總表" sheetId="1" r:id="rId1"/>
+    <sheet name="庫存明細總表 | Inventory Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
